--- a/SHET/GZ001/gzsign1.xlsx
+++ b/SHET/GZ001/gzsign1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\GZ001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C850E6E1-D669-4BCD-B868-317052250499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EC823C-5B7F-4464-AD55-154455CFE26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="21">
   <si>
     <t>Название таблицы</t>
   </si>
@@ -73,19 +73,25 @@
     <t>ФК</t>
   </si>
   <si>
-    <t>ЖС</t>
-  </si>
-  <si>
     <t>X:161, X:221</t>
   </si>
   <si>
     <t>X:75, X:79</t>
   </si>
   <si>
-    <t>Воздействие</t>
-  </si>
-  <si>
     <t>Срабатывание выходного реле при введенном SA1</t>
+  </si>
+  <si>
+    <t>Вход для проверки</t>
+  </si>
+  <si>
+    <t>Выход для контроля</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>ТС</t>
   </si>
 </sst>
 </file>
@@ -121,9 +127,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -407,154 +416,173 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="49.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.5703125" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="1">
+      <c r="C2" s="2"/>
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>2</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>3</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
@@ -562,14 +590,18 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SHET/GZ001/gzsign1.xlsx
+++ b/SHET/GZ001/gzsign1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WWWW\protocols\SHET\GZ001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EC823C-5B7F-4464-AD55-154455CFE26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7726775E-EEC1-43A4-8619-D5237E541C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9390" yWindow="1860" windowWidth="15000" windowHeight="7575" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -79,9 +79,6 @@
     <t>X:75, X:79</t>
   </si>
   <si>
-    <t>Срабатывание выходного реле при введенном SA1</t>
-  </si>
-  <si>
     <t>Вход для проверки</t>
   </si>
   <si>
@@ -92,6 +89,9 @@
   </si>
   <si>
     <t>ТС</t>
+  </si>
+  <si>
+    <t>Срабатывание выходного реле</t>
   </si>
 </sst>
 </file>
@@ -426,13 +426,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -466,7 +466,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>8</v>
@@ -489,7 +489,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
@@ -529,13 +529,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>8</v>
@@ -552,13 +552,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>8</v>
@@ -575,10 +575,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
